--- a/meu-projeto/docs/clientes/torre-1/campaigns/data.xlsx
+++ b/meu-projeto/docs/clientes/torre-1/campaigns/data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>ID da Campanha</t>
   </si>
@@ -84,13 +84,7 @@
     <t>SEGUIDORES [Engajamento] [SYRA] [CBO]</t>
   </si>
   <si>
-    <t>ACTIVE</t>
-  </si>
-  <si>
     <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>✅ Ativa</t>
   </si>
   <si>
     <t>23849193772700137</t>
@@ -164,7 +158,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,11 +180,6 @@
         <fgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -204,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -215,7 +204,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,8 +663,8 @@
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>23</v>
+      <c r="C3" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -685,7 +673,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -712,27 +700,27 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="8">
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -788,13 +776,13 @@
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -803,7 +791,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
@@ -818,30 +806,30 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -859,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -886,19 +874,19 @@
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>6</v>
@@ -916,24 +904,24 @@
         <v>2</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -948,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
